--- a/docs/Mapping_casi_uso/matrimoni/Matr_009.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_009.xlsx
@@ -845,7 +845,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -854,7 +854,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -863,7 +863,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -872,7 +872,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -881,13 +881,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Figlio</t>
@@ -926,7 +926,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Atto Nascita Figlio</t>
@@ -944,13 +944,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Assenso figlio</t>
@@ -977,7 +977,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dati Riconoscimento - Generalità discendenti - Matrimoni</t>
@@ -1124,13 +1124,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1234,7 +1234,7 @@
     <col min="4" max="4" width="68.45703125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="32.48828125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="119.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10465,10 +10465,10 @@
         <v>275</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>276</v>
@@ -11109,10 +11109,10 @@
         <v>278</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>279</v>
@@ -11753,10 +11753,10 @@
         <v>281</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>282</v>
@@ -12397,10 +12397,10 @@
         <v>284</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D486" s="2" t="s">
         <v>285</v>
@@ -13041,10 +13041,10 @@
         <v>287</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>288</v>
@@ -13685,10 +13685,10 @@
         <v>290</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D542" s="2" t="s">
         <v>288</v>
@@ -16146,10 +16146,10 @@
         <v>308</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D649" s="2" t="s">
         <v>309</v>
@@ -16790,10 +16790,10 @@
         <v>311</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D677" s="2" t="s">
         <v>309</v>
@@ -18757,7 +18757,7 @@
         <v>371</v>
       </c>
       <c r="F762" s="2" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="G762" s="2" t="s">
         <v>62</v>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_009.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_009.xlsx
@@ -8582,7 +8582,7 @@
         <v>205</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>242</v>
